--- a/config/xlsx/rewards.xlsx
+++ b/config/xlsx/rewards.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -481,7 +481,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>4:100</t>
+          <t>3:10</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
@@ -638,6 +638,33 @@
         <is>
           <t>25001:1</t>
         </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n" s="2">
+        <v>3</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" t="str" s="3">
+        <v>1701:1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n" s="2">
+        <v>4</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" t="str" s="3">
+        <v>1702:1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n" s="2">
+        <v>5</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" t="str" s="3">
+        <v>1703:1</v>
       </c>
     </row>
   </sheetData>
